--- a/calib/pose.xlsx
+++ b/calib/pose.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,502 +462,462 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>180</v>
+        <v>87.94124430050003</v>
       </c>
       <c r="B2" t="n">
-        <v>4.900218410423993e-15</v>
+        <v>6.278787856107106</v>
       </c>
       <c r="C2" t="n">
-        <v>153</v>
+        <v>177.6730725458355</v>
       </c>
       <c r="D2" t="n">
-        <v>-453.9800053549399</v>
+        <v>-483.7116397890059</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99888983208504</v>
+        <v>21.92291835289027</v>
       </c>
       <c r="F2" t="n">
-        <v>539.849693481159</v>
+        <v>617.7110381338123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-171.99951373815</v>
+        <v>88.1179217797222</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.001733681291856916</v>
+        <v>1.771667958723341</v>
       </c>
       <c r="C3" t="n">
-        <v>153.0006587530683</v>
+        <v>179.0485821176242</v>
       </c>
       <c r="D3" t="n">
-        <v>-453.9890443415414</v>
+        <v>-454.5158182790167</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99897719685922</v>
+        <v>13.67233181267238</v>
       </c>
       <c r="F3" t="n">
-        <v>539.8645459479994</v>
+        <v>529.7431835379922</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>170</v>
+        <v>93.18901725985658</v>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>1.786318336109558</v>
       </c>
       <c r="C4" t="n">
-        <v>153.001</v>
+        <v>-175.1182617385601</v>
       </c>
       <c r="D4" t="n">
-        <v>-454</v>
+        <v>-451.9302851688608</v>
       </c>
       <c r="E4" t="n">
-        <v>-50.001</v>
+        <v>-48.99159273746172</v>
       </c>
       <c r="F4" t="n">
-        <v>540</v>
+        <v>530.0137186033785</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>175</v>
+        <v>93.11925892284869</v>
       </c>
       <c r="B5" t="n">
-        <v>-0</v>
+        <v>6.442552329082832</v>
       </c>
       <c r="C5" t="n">
-        <v>153</v>
+        <v>162.342689206081</v>
       </c>
       <c r="D5" t="n">
-        <v>-453.999</v>
+        <v>-435.3965893793435</v>
       </c>
       <c r="E5" t="n">
-        <v>-49.998</v>
+        <v>130.1201295854949</v>
       </c>
       <c r="F5" t="n">
-        <v>540</v>
+        <v>529.6649033780114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>170</v>
+        <v>93.62550615563836</v>
       </c>
       <c r="B6" t="n">
-        <v>-0</v>
+        <v>-18.9843665927318</v>
       </c>
       <c r="C6" t="n">
-        <v>153</v>
+        <v>161.9965852484787</v>
       </c>
       <c r="D6" t="n">
-        <v>-413.997</v>
+        <v>-228.8260266145543</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.997</v>
+        <v>66.81804758458115</v>
       </c>
       <c r="F6" t="n">
-        <v>539.999</v>
+        <v>571.790112895057</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>165</v>
+        <v>73.37232135896268</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-17.2959461368647</v>
       </c>
       <c r="C7" t="n">
-        <v>153</v>
+        <v>-175.4773695562471</v>
       </c>
       <c r="D7" t="n">
-        <v>-454.001</v>
+        <v>-235.8543702649201</v>
       </c>
       <c r="E7" t="n">
-        <v>-50.001</v>
+        <v>14.55356237549628</v>
       </c>
       <c r="F7" t="n">
-        <v>539.999</v>
+        <v>559.6546528474668</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>170</v>
+        <v>101.0782132154078</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-7.167405492323417</v>
       </c>
       <c r="C8" t="n">
-        <v>153</v>
+        <v>165.3816297220114</v>
       </c>
       <c r="D8" t="n">
-        <v>-494.001</v>
+        <v>-269.2060048984859</v>
       </c>
       <c r="E8" t="n">
-        <v>-90.002</v>
+        <v>55.25026374338949</v>
       </c>
       <c r="F8" t="n">
-        <v>539.995</v>
+        <v>600.8860653608027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>170</v>
+        <v>95.3226445442819</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>-6.746135348008303</v>
       </c>
       <c r="C9" t="n">
-        <v>153</v>
+        <v>169.0128118613362</v>
       </c>
       <c r="D9" t="n">
-        <v>-453.997</v>
+        <v>-259.3003067891103</v>
       </c>
       <c r="E9" t="n">
-        <v>-49.997</v>
+        <v>53.41538941832714</v>
       </c>
       <c r="F9" t="n">
-        <v>540</v>
+        <v>797.3041921773587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>170</v>
+        <v>95.27844117796857</v>
       </c>
       <c r="B10" t="n">
-        <v>-0</v>
+        <v>-17.77884081255499</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>164.6870668545606</v>
       </c>
       <c r="D10" t="n">
-        <v>-413.999</v>
+        <v>-235.803299960311</v>
       </c>
       <c r="E10" t="n">
-        <v>-90.001</v>
+        <v>48.5793391476434</v>
       </c>
       <c r="F10" t="n">
-        <v>540.001</v>
+        <v>478.850092797622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>169.999</v>
+        <v>58.56529752793086</v>
       </c>
       <c r="B11" t="n">
-        <v>-8</v>
+        <v>-7.571131185883659</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>-145.7762028844013</v>
       </c>
       <c r="D11" t="n">
-        <v>-454.002</v>
+        <v>-246.8988838325292</v>
       </c>
       <c r="E11" t="n">
-        <v>-49.997</v>
+        <v>-97.74421417990942</v>
       </c>
       <c r="F11" t="n">
-        <v>540.001</v>
+        <v>557.9868500723427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>170</v>
+        <v>58.91364398535772</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0.03636641035334361</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>-137.6812284851893</v>
       </c>
       <c r="D12" t="n">
-        <v>-494.002</v>
+        <v>-219.3908837980952</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.999000000000001</v>
+        <v>-148.7566850357454</v>
       </c>
       <c r="F12" t="n">
-        <v>540</v>
+        <v>555.9228376903162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>170</v>
+        <v>100.9628460021615</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-6.658491965583071</v>
       </c>
       <c r="C13" t="n">
-        <v>161</v>
+        <v>154.8250908109928</v>
       </c>
       <c r="D13" t="n">
-        <v>-453.997</v>
+        <v>-280.4569086357032</v>
       </c>
       <c r="E13" t="n">
-        <v>-49.999</v>
+        <v>110.2827090542243</v>
       </c>
       <c r="F13" t="n">
-        <v>540.001</v>
+        <v>581.7071687887135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>170</v>
+        <v>120.8941039896343</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.001</v>
+        <v>-1.954339871350139</v>
       </c>
       <c r="C14" t="n">
-        <v>145</v>
+        <v>148.1886053598147</v>
       </c>
       <c r="D14" t="n">
-        <v>-454.002</v>
+        <v>-279.2890160432329</v>
       </c>
       <c r="E14" t="n">
-        <v>-49.998</v>
+        <v>117.1729249256568</v>
       </c>
       <c r="F14" t="n">
-        <v>540.004</v>
+        <v>578.2512699475238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>175</v>
+        <v>90.30645623677108</v>
       </c>
       <c r="B15" t="n">
-        <v>7.999</v>
+        <v>-18.60150810056543</v>
       </c>
       <c r="C15" t="n">
-        <v>153</v>
+        <v>-177.308071285276</v>
       </c>
       <c r="D15" t="n">
-        <v>-433.999</v>
+        <v>-247.7123614853523</v>
       </c>
       <c r="E15" t="n">
-        <v>-49.997</v>
+        <v>-12.48788476791343</v>
       </c>
       <c r="F15" t="n">
-        <v>540</v>
+        <v>508.7698483769457</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>164.999</v>
+        <v>90.35265361328547</v>
       </c>
       <c r="B16" t="n">
-        <v>-8</v>
+        <v>-33.83748060304665</v>
       </c>
       <c r="C16" t="n">
-        <v>153</v>
+        <v>-177.2981891885556</v>
       </c>
       <c r="D16" t="n">
-        <v>-474.001</v>
+        <v>-140.5529724542522</v>
       </c>
       <c r="E16" t="n">
-        <v>-50</v>
+        <v>-7.132403517287434</v>
       </c>
       <c r="F16" t="n">
-        <v>540.002</v>
+        <v>542.2904831926378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>165</v>
+        <v>90.30683574808367</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>-16.21296154089606</v>
       </c>
       <c r="C17" t="n">
-        <v>153</v>
+        <v>-177.1119578549639</v>
       </c>
       <c r="D17" t="n">
-        <v>-454.004</v>
+        <v>-126.368418898606</v>
       </c>
       <c r="E17" t="n">
-        <v>-29.998</v>
+        <v>-6.408181573551945</v>
       </c>
       <c r="F17" t="n">
-        <v>540</v>
+        <v>675.7634557587903</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>175</v>
+        <v>69.62144365052551</v>
       </c>
       <c r="B18" t="n">
-        <v>-8</v>
+        <v>-9.834207373830772</v>
       </c>
       <c r="C18" t="n">
-        <v>153</v>
+        <v>-165.8832093547143</v>
       </c>
       <c r="D18" t="n">
-        <v>-453.999</v>
+        <v>-311.3089160832768</v>
       </c>
       <c r="E18" t="n">
-        <v>-70.001</v>
+        <v>-14.69184672375471</v>
       </c>
       <c r="F18" t="n">
-        <v>540.001</v>
+        <v>525.817049561184</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>175</v>
+        <v>92.96382877395405</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-8.430620690371155</v>
       </c>
       <c r="C19" t="n">
-        <v>161</v>
+        <v>172.1282631220171</v>
       </c>
       <c r="D19" t="n">
-        <v>-454</v>
+        <v>-310.9911871291432</v>
       </c>
       <c r="E19" t="n">
-        <v>-49.999</v>
+        <v>34.72936810545198</v>
       </c>
       <c r="F19" t="n">
-        <v>439.998</v>
+        <v>529.2399127232554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>165</v>
+        <v>115.9607743163194</v>
       </c>
       <c r="B20" t="n">
-        <v>-0</v>
+        <v>-1.210527578986302</v>
       </c>
       <c r="C20" t="n">
-        <v>145</v>
+        <v>156.1657590327262</v>
       </c>
       <c r="D20" t="n">
-        <v>-454.003</v>
+        <v>-318.2910560424151</v>
       </c>
       <c r="E20" t="n">
-        <v>-50.002</v>
+        <v>102.8297495519511</v>
       </c>
       <c r="F20" t="n">
-        <v>540.001</v>
+        <v>608.7982175442775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>165</v>
+        <v>97.78842074315318</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-8.599041110275406</v>
       </c>
       <c r="C21" t="n">
-        <v>161</v>
+        <v>157.5689760878208</v>
       </c>
       <c r="D21" t="n">
-        <v>-453.999</v>
+        <v>-272.3364849080554</v>
       </c>
       <c r="E21" t="n">
-        <v>-50.001</v>
+        <v>99.57477459502948</v>
       </c>
       <c r="F21" t="n">
-        <v>439.995</v>
+        <v>606.4496424593254</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>175</v>
+        <v>70.36864931899397</v>
       </c>
       <c r="B22" t="n">
-        <v>-0</v>
+        <v>-15.53248908859515</v>
       </c>
       <c r="C22" t="n">
-        <v>145</v>
+        <v>-166.4538821997957</v>
       </c>
       <c r="D22" t="n">
-        <v>-453.999</v>
+        <v>-283.1005779516201</v>
       </c>
       <c r="E22" t="n">
-        <v>-49.999</v>
+        <v>-18.19317701121158</v>
       </c>
       <c r="F22" t="n">
-        <v>540.005</v>
+        <v>570.6173520210575</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>169.999</v>
+        <v>87.5135876200416</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>-12.20421264783097</v>
       </c>
       <c r="C23" t="n">
-        <v>161</v>
+        <v>-176.8136092091251</v>
       </c>
       <c r="D23" t="n">
-        <v>-454.001</v>
+        <v>-252.7869486963793</v>
       </c>
       <c r="E23" t="n">
-        <v>-50.001</v>
+        <v>-16.41345602752753</v>
       </c>
       <c r="F23" t="n">
-        <v>439.997</v>
+        <v>891.5407918019248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>170</v>
+        <v>76.00874182631958</v>
       </c>
       <c r="B24" t="n">
-        <v>-8.000999999999999</v>
+        <v>-17.8145257561053</v>
       </c>
       <c r="C24" t="n">
-        <v>145</v>
+        <v>-177.8413119885493</v>
       </c>
       <c r="D24" t="n">
-        <v>-453.999</v>
+        <v>-252.7320732510385</v>
       </c>
       <c r="E24" t="n">
-        <v>-50.001</v>
+        <v>-16.28143868309718</v>
       </c>
       <c r="F24" t="n">
-        <v>540.006</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>169.999</v>
-      </c>
-      <c r="B25" t="n">
-        <v>-8</v>
-      </c>
-      <c r="C25" t="n">
-        <v>161</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-454.001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-49.997</v>
-      </c>
-      <c r="F25" t="n">
-        <v>439.997</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>169.999</v>
-      </c>
-      <c r="B26" t="n">
-        <v>8</v>
-      </c>
-      <c r="C26" t="n">
-        <v>145</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-454.001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-49.997</v>
-      </c>
-      <c r="F26" t="n">
-        <v>539.999</v>
+        <v>891.4767530181933</v>
       </c>
     </row>
   </sheetData>
